--- a/ROUTE_1_PATH1_ECE_MECH_FC_CY_AUDI/PATH1_FINAL_ODK.xlsx
+++ b/ROUTE_1_PATH1_ECE_MECH_FC_CY_AUDI/PATH1_FINAL_ODK.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:J65"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,15 +418,18 @@
         <v>required</v>
       </c>
       <c r="F1" t="str">
+        <v>required_message</v>
+      </c>
+      <c r="G1" t="str">
         <v>constraint</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>constraint_message</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>relevant</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>media::audio</v>
       </c>
     </row>
@@ -446,37 +449,74 @@
         <v>note</v>
       </c>
       <c r="B3" t="str">
-        <v>start_note</v>
+        <v>instructions_rules_note</v>
       </c>
       <c r="C3" t="str" xml:space="preserve">
         <v xml:space="preserve">🏆 FINAL CLUE — PATH 1
+TREASURE HUNT FOR FRESHERS 2026
 Welcome to PATH 1 of the Final Clue Treasure Hunt!
-Navigate through the campus stations by solving clues, completing physical &amp; mental challenges, finding hidden objects, and getting verified by volunteers.
-⚠️ IMPORTANT RULES:
-• All questions and photo uploads are MANDATORY.
-• All text answers and codes must be entered in UPPERCASE ONLY.
-• Each station unlocks only after entering the correct answer or volunteer code.</v>
+📜 INSTRUCTIONS — RULES AND REGULATIONS:
+• Participants must report to the designated starting point [5-10 minutes] before the event begins.
+• Each team must consist of [3-4] members.
+• At least one member of the team should have an Android phone.
+• Each team will receive the first clue at the beginning of the event.
+• Teams must solve each clue to find the location of the next clue.
+• Clues must be solved in the given sequence.
+• Teams are not allowed to take, hide, damage, or tamper with clues belonging to other teams.
+• Teams must remain within the designated event area.
+• Running in unsafe areas and restricted zones is prohibited.
+• Participants must not enter restricted areas or disturb ongoing events/classes.
+• Physical force, pushing, blocking, or interfering with other teams is strictly prohibited.
+• Only ONE phone containing ODK Collect is allowed per team.
+• No use of Wi-Fi unless specified... else disqualified!
+• Participants must not damage or move any property while searching for clues.
+• Teams must follow instructions given by volunteers and organizers at all times.
+• Asking people outside the team for answers or assistance is not allowed.
+• Teams must not follow, copy, or deliberately interfere with another team's progress.
+• Tampering with clues, cheating, entering restricted areas, or intentionally misleading other teams may result in immediate disqualification.
+• Participants must report to the designated starting point [10–15 minutes] before the event begins.
+• The Organizing Committee will not be responsible for the loss or damage of any personal belongings of the participants.
+🏆 TEAM QUALIFICATION RULES (PER PATH):
+• 5 Rounds in each path
+• Round 1 ➔ Round 2: First 25 teams proceed
+• Round 2 ➔ Round 3: Next 15 teams proceed
+• Round 3 ➔ Round 4: Next 7 teams proceed
+• Round 4 ➔ Round 5: Next 2 teams proceed
+from each path
+⚠️ MANDATORY RESPONSE &amp; CAPS ONLY RULES:
+• Every single question and upload is strictly MANDATORY.
+• All text answers and volunteer clearance codes must be entered in UPPERCASE (CAPS ONLY).
+• Lowercase letters will be rejected.</v>
       </c>
       <c r="D3" t="str">
-        <v>Read all instructions carefully before starting.</v>
+        <v>Read all rules and instructions carefully.</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>note</v>
+        <v>text</v>
       </c>
       <c r="B4" t="str">
-        <v>caps_rules_note</v>
+        <v>team_id</v>
       </c>
       <c r="C4" t="str" xml:space="preserve">
-        <v xml:space="preserve">⚠️ MANDATORY RESPONSE &amp; CAPS ONLY RULES
-Enter code in caps on every input.
-Lowercase answers will be rejected by validation.
-Photo uploads are strictly mandatory for physical &amp; object checkpoints.
-Do not use internet search engines, AI tools, or Wi-Fi.</v>
+        <v xml:space="preserve">Enter Team ID / Team Name (MANDATORY)
+Enter code in caps</v>
       </c>
       <c r="D4" t="str">
-        <v>Always type answers in CAPS.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E4" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F4" t="str">
+        <v>❌ Team ID is mandatory. Please enter your Team ID in UPPERCASE.</v>
+      </c>
+      <c r="G4" t="str">
+        <v>regex(., '^[A-Z0-9\-_ ]+$')</v>
+      </c>
+      <c r="H4" t="str">
+        <v>❌ Please enter Team ID in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -484,11 +524,11 @@
         <v>text</v>
       </c>
       <c r="B5" t="str">
-        <v>team_id</v>
+        <v>team_leader_name</v>
       </c>
       <c r="C5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Team ID / Team Name
-Enter code in caps</v>
+        <v xml:space="preserve">Enter Team Leader Name (MANDATORY)
+Enter in caps</v>
       </c>
       <c r="D5" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
@@ -497,295 +537,305 @@
         <v>yes</v>
       </c>
       <c r="F5" t="str">
-        <v>regex(., '^[A-Z0-9\-_ ]+$')</v>
+        <v>❌ Team Leader Name is mandatory. Please enter in UPPERCASE.</v>
       </c>
       <c r="G5" t="str">
-        <v>❌ Please enter Team ID in UPPERCASE (CAPS ONLY).</v>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
+        <v>regex(., '^[A-Z ]+$')</v>
+      </c>
+      <c r="H5" t="str">
+        <v>❌ Please enter Team Leader Name in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="str">
-        <v>text</v>
-      </c>
-      <c r="B6" t="str">
-        <v>team_leader_name</v>
-      </c>
-      <c r="C6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Team Leader Name
-Enter in caps</v>
-      </c>
-      <c r="D6" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E6" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F6" t="str">
-        <v>regex(., '^[A-Z ]+$')</v>
-      </c>
-      <c r="G6" t="str">
-        <v>❌ Please enter Team Leader Name in UPPERCASE (CAPS ONLY).</v>
+        <v>end_group</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>begin_group</v>
+      </c>
+      <c r="B7" t="str">
+        <v>r1_group</v>
+      </c>
+      <c r="C7" t="str">
+        <v>ROUND 1</v>
+      </c>
+      <c r="I7" t="str">
+        <v>${team_id} != '' and ${team_leader_name} != ''</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>begin_group</v>
+        <v>note</v>
       </c>
       <c r="B8" t="str">
-        <v>r1_group</v>
-      </c>
-      <c r="C8" t="str">
-        <v>ROUND 1 — OBJECT FINDING</v>
-      </c>
-      <c r="H8" t="str">
-        <v>${team_id} != '' and ${team_leader_name} != ''</v>
+        <v>r1_intro</v>
+      </c>
+      <c r="C8" t="str" xml:space="preserve">
+        <v xml:space="preserve">📍 ROUND 1
+Search the block to locate the assigned hidden object.
+Upload a clear photo of the object and ask a volunteer with a LUMINUS ID card nearby for the round completion code.
+Enter code in caps</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Locate object, take photo, and ask volunteer for code.</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>note</v>
+        <v>image</v>
       </c>
       <c r="B9" t="str">
-        <v>r1_intro</v>
+        <v>r1_object_photo</v>
       </c>
       <c r="C9" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 1: 🧩 OBJECT FINDING
-Challenge: Find one of the assigned hidden objects located in this block.
-Instructions:
-1. Search the block to locate the assigned hidden object.
-2. Take a clear photo of the object.
-3. Show the photo to the station volunteer to receive your verification code.
-Enter code in caps</v>
+        <v xml:space="preserve">📸 Upload Photo of the Discovered Hidden Object (MANDATORY)
+Photo upload is mandatory</v>
       </c>
       <c r="D9" t="str">
-        <v>Search for the assigned hidden object.</v>
+        <v>Take a clear, well-lit photo of the discovered object.</v>
+      </c>
+      <c r="E9" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F9" t="str">
+        <v>❌ Photo upload of the hidden object is strictly mandatory.</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>image</v>
+        <v>text</v>
       </c>
       <c r="B10" t="str">
-        <v>r1_object_photo</v>
+        <v>r1_code</v>
       </c>
       <c r="C10" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of the Discovered Hidden Object
-Photo upload is mandatory</v>
+        <v xml:space="preserve">Enter Volunteer Verification Code (MANDATORY)
+Enter code in caps</v>
       </c>
       <c r="D10" t="str">
-        <v>Take a clear, well-lit photo of the discovered object.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
       <c r="E10" t="str">
         <v>yes</v>
       </c>
-    </row>
-    <row r="11" xml:space="preserve">
+      <c r="F10" t="str">
+        <v>❌ Volunteer verification code is mandatory.</v>
+      </c>
+      <c r="G10" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'R1-P1EC'</v>
+      </c>
+      <c r="H10" t="str">
+        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer with a LUMINUS ID card.</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="str">
-        <v>text</v>
-      </c>
-      <c r="B11" t="str">
-        <v>r1_code</v>
-      </c>
-      <c r="C11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Verification Code
-Enter code in caps</v>
-      </c>
-      <c r="D11" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E11" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F11" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'R1-P1EC'</v>
-      </c>
-      <c r="G11" t="str">
-        <v>❌ Incorrect code. Enter the code in CAPS provided by the volunteer.</v>
+        <v>end_group</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>begin_group</v>
+      </c>
+      <c r="B12" t="str">
+        <v>r2_loc_group</v>
+      </c>
+      <c r="C12" t="str">
+        <v>ROUND 2 LOCATION CLUE</v>
+      </c>
+      <c r="I12" t="str">
+        <v>normalize-space(${r1_code}) = 'R1-P1EC'</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
-        <v>begin_group</v>
+        <v>note</v>
       </c>
       <c r="B13" t="str">
-        <v>r2_loc_group</v>
-      </c>
-      <c r="C13" t="str">
-        <v>ROUND 2 LOCATION CLUE</v>
-      </c>
-      <c r="H13" t="str">
-        <v>translate(normalize-space(${r1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'R1-P1EC'</v>
+        <v>r2_audio_note</v>
+      </c>
+      <c r="C13" t="str" xml:space="preserve">
+        <v xml:space="preserve">🔊 Listen carefully to the sound and identify the academic block related to this sound...
+Enter code in caps</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Play audio and identify the academic block.</v>
+      </c>
+      <c r="J13" t="str">
+        <v>engine_sound.mpeg</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
       <c r="A14" t="str">
-        <v>note</v>
+        <v>text</v>
       </c>
       <c r="B14" t="str">
-        <v>r2_sound_note</v>
+        <v>r2_sound_destination</v>
       </c>
       <c r="C14" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 2 LOCATION CLUE: ENGINE SOUND CHALLENGE
-🔊 Listen carefully to the engine audio clip below.
-Identify what sound is playing and deduce the campus block where your next destination is located.
+        <v xml:space="preserve">Which academic block is related to this sound? (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D14" t="str">
-        <v>Play audio and identify the destination block.</v>
-      </c>
-      <c r="I14" t="str">
-        <v>engine_sound.mpeg</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E14" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F14" t="str">
+        <v>❌ Answering the academic block is mandatory.</v>
+      </c>
+      <c r="G14" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MECH' or normalize-space(.) = 'MECHANICAL BLOCK' or normalize-space(.) = 'MECH BLOCK' or normalize-space(.) = 'MECHANICAL')</v>
+      </c>
+      <c r="H14" t="str">
+        <v>❌ Incorrect academic block. Listen to the sound and enter the block name in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
       <c r="A15" t="str">
-        <v>text</v>
+        <v>note</v>
       </c>
       <c r="B15" t="str">
-        <v>r2_sound_destination</v>
+        <v>r2_proceed_note</v>
       </c>
       <c r="C15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Which campus block does this engine sound direct your team to?
+        <v xml:space="preserve">🏃 Proceed to the academic block you identified!
+Find the volunteer with a LUMINUS ID card nearby and ask them for the code to start your challenge.
 Enter code in caps</v>
       </c>
       <c r="D15" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E15" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F15" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECHANICAL' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH BLOCK'</v>
-      </c>
-      <c r="G15" t="str">
-        <v>❌ Incorrect block name. Listen to the engine sound and enter the block name in CAPS.</v>
+        <v>Go to the block and ask volunteer for start code.</v>
+      </c>
+      <c r="I15" t="str">
+        <v>normalize-space(${r2_sound_destination}) = 'MECH' or normalize-space(${r2_sound_destination}) = 'MECHANICAL BLOCK' or normalize-space(${r2_sound_destination}) = 'MECH BLOCK' or normalize-space(${r2_sound_destination}) = 'MECHANICAL'</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
       <c r="A16" t="str">
-        <v>note</v>
+        <v>text</v>
       </c>
       <c r="B16" t="str">
-        <v>r2_arrival_note</v>
+        <v>r2_sound_pass</v>
       </c>
       <c r="C16" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏃 PROCEED TO MECH BLOCK
-Report immediately to the MECH block.
-Show this screen to the volunteer to receive your arrival code.
-Enter code in caps</v>
+        <v xml:space="preserve">Enter Challenge Start Code from Volunteer (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D16" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E16" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F16" t="str">
+        <v>❌ Challenge start code is mandatory.</v>
+      </c>
+      <c r="G16" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'SOUND-PASS'</v>
       </c>
       <c r="H16" t="str">
-        <v>translate(normalize-space(${r2_sound_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH' or translate(normalize-space(${r2_sound_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECHANICAL' or translate(normalize-space(${r2_sound_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH BLOCK'</v>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
+        <v>❌ Incorrect start code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+      <c r="I16" t="str">
+        <v>normalize-space(${r2_sound_destination}) = 'MECH' or normalize-space(${r2_sound_destination}) = 'MECHANICAL BLOCK' or normalize-space(${r2_sound_destination}) = 'MECH BLOCK' or normalize-space(${r2_sound_destination}) = 'MECHANICAL'</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="str">
-        <v>text</v>
-      </c>
-      <c r="B17" t="str">
-        <v>r2_sound_pass</v>
-      </c>
-      <c r="C17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter MECH Arrival Verification Code
-Enter code in caps</v>
-      </c>
-      <c r="D17" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E17" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F17" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'SOUND-PASS'</v>
-      </c>
-      <c r="G17" t="str">
-        <v>❌ Incorrect code. Enter the code in CAPS provided by the volunteer.</v>
-      </c>
-      <c r="H17" t="str">
-        <v>translate(normalize-space(${r2_sound_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH' or translate(normalize-space(${r2_sound_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECHANICAL' or translate(normalize-space(${r2_sound_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH BLOCK'</v>
+        <v>end_group</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>begin_group</v>
+      </c>
+      <c r="B18" t="str">
+        <v>r2_mini_group</v>
+      </c>
+      <c r="C18" t="str">
+        <v>ROUND 2 — MINI CHALLENGE</v>
+      </c>
+      <c r="I18" t="str">
+        <v>normalize-space(${r2_sound_pass}) = 'SOUND-PASS'</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
       <c r="A19" t="str">
+        <v>select_one r2_variant_list</v>
+      </c>
+      <c r="B19" t="str">
+        <v>r2_variant_selected</v>
+      </c>
+      <c r="C19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Select the Challenge Variant Assigned to Your Team (MANDATORY)
+Mandatory selection</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Choose Variant A (Human Poses) or Variant B (Paper Ball)</v>
+      </c>
+      <c r="E19" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F19" t="str">
+        <v>❌ Selecting your assigned challenge variant is mandatory.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B19" t="str">
-        <v>r2_mini_group</v>
-      </c>
-      <c r="C19" t="str">
-        <v>ROUND 2 — MINI CHALLENGE</v>
-      </c>
-      <c r="H19" t="str">
-        <v>translate(normalize-space(${r2_sound_pass}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'SOUND-PASS'</v>
-      </c>
-    </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20" t="str">
-        <v>select_one mech_task_list</v>
-      </c>
       <c r="B20" t="str">
-        <v>r2_chit_selected</v>
-      </c>
-      <c r="C20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Select the Mini-Challenge Chit Picked by Your Team
-Mandatory selection</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Choose the variant assigned by the chit you drew</v>
-      </c>
-      <c r="E20" t="str">
-        <v>yes</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>r2_var_a_group</v>
+      </c>
+      <c r="C20" t="str">
+        <v>VARIANT A — HUMAN POSES</v>
+      </c>
+      <c r="I20" t="str">
+        <v>${r2_variant_selected} = 'var_a'</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
       <c r="A21" t="str">
-        <v>begin_group</v>
+        <v>note</v>
       </c>
       <c r="B21" t="str">
-        <v>r2_var1_group</v>
-      </c>
-      <c r="C21" t="str">
-        <v>VARIANT 1 — HUMAN SHAPE</v>
-      </c>
-      <c r="H21" t="str">
-        <v>${r2_chit_selected} = 'var1'</v>
+        <v>r2_var_a_pose_note</v>
+      </c>
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">🧍 VARIANT A: HUMAN POSES
+Instructions:
+1. Refer to the poses shown by the volunteer.
+2. Perform any 4 poses with your team.
+3. Take and upload photos of the 4 poses one by one below (all 4 uploads are mandatory).
+4. Show the poses to the volunteer to receive your challenge completion code.
+Enter code in caps</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Perform any 4 poses shown by volunteer and upload 4 photos.</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
       <c r="A22" t="str">
-        <v>note</v>
+        <v>image</v>
       </c>
       <c r="B22" t="str">
-        <v>r2_var1_pose_note</v>
+        <v>r2_var_a_photo_1</v>
       </c>
       <c r="C22" t="str" xml:space="preserve">
-        <v xml:space="preserve">🧍 MINI-CHALLENGE: HUMAN SHAPE
-Participants must recreate the poses shown on the poses page provided by the station volunteers using all four team members.
-Instructions:
-1. Refer to the poses card / page provided by the station volunteers.
-2. Recreate the assigned poses accurately with your 4 team members.
-3. Take photos of all 4 members performing their poses.
-4. Upload the 4 photos below (all 4 uploads are mandatory).
-5. Show the poses to the volunteer to receive the verification code.
-Enter code in caps</v>
+        <v xml:space="preserve">📸 Upload Photo of Pose 1 (MANDATORY)
+Photo upload is mandatory</v>
       </c>
       <c r="D22" t="str">
-        <v>Refer to the poses page provided by the volunteers.</v>
+        <v>Upload clear photo of team pose 1.</v>
+      </c>
+      <c r="E22" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F22" t="str">
+        <v>❌ Uploading photo of Pose 1 is mandatory.</v>
       </c>
     </row>
     <row r="23" xml:space="preserve">
@@ -793,17 +843,20 @@
         <v>image</v>
       </c>
       <c r="B23" t="str">
-        <v>r2_var1_pose_photo_1</v>
+        <v>r2_var_a_photo_2</v>
       </c>
       <c r="C23" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo 1 of Team Member Pose (Mandatory)
+        <v xml:space="preserve">📸 Upload Photo of Pose 2 (MANDATORY)
 Photo upload is mandatory</v>
       </c>
       <c r="D23" t="str">
-        <v>Upload clear photo of team member 1 pose.</v>
+        <v>Upload clear photo of team pose 2.</v>
       </c>
       <c r="E23" t="str">
         <v>yes</v>
+      </c>
+      <c r="F23" t="str">
+        <v>❌ Uploading photo of Pose 2 is mandatory.</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
@@ -811,17 +864,20 @@
         <v>image</v>
       </c>
       <c r="B24" t="str">
-        <v>r2_var1_pose_photo_2</v>
+        <v>r2_var_a_photo_3</v>
       </c>
       <c r="C24" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo 2 of Team Member Pose (Mandatory)
+        <v xml:space="preserve">📸 Upload Photo of Pose 3 (MANDATORY)
 Photo upload is mandatory</v>
       </c>
       <c r="D24" t="str">
-        <v>Upload clear photo of team member 2 pose.</v>
+        <v>Upload clear photo of team pose 3.</v>
       </c>
       <c r="E24" t="str">
         <v>yes</v>
+      </c>
+      <c r="F24" t="str">
+        <v>❌ Uploading photo of Pose 3 is mandatory.</v>
       </c>
     </row>
     <row r="25" xml:space="preserve">
@@ -829,122 +885,117 @@
         <v>image</v>
       </c>
       <c r="B25" t="str">
-        <v>r2_var1_pose_photo_3</v>
+        <v>r2_var_a_photo_4</v>
       </c>
       <c r="C25" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo 3 of Team Member Pose (Mandatory)
+        <v xml:space="preserve">📸 Upload Photo of Pose 4 (MANDATORY)
 Photo upload is mandatory</v>
       </c>
       <c r="D25" t="str">
-        <v>Upload clear photo of team member 3 pose.</v>
+        <v>Upload clear photo of team pose 4.</v>
       </c>
       <c r="E25" t="str">
         <v>yes</v>
+      </c>
+      <c r="F25" t="str">
+        <v>❌ Uploading photo of Pose 4 is mandatory.</v>
       </c>
     </row>
     <row r="26" xml:space="preserve">
       <c r="A26" t="str">
-        <v>image</v>
+        <v>text</v>
       </c>
       <c r="B26" t="str">
-        <v>r2_var1_pose_photo_4</v>
+        <v>r2_var_a_volunteer_code</v>
       </c>
       <c r="C26" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo 4 of Team Member Pose (Mandatory)
-Photo upload is mandatory</v>
+        <v xml:space="preserve">Enter Challenge Completion Code from Volunteer (MANDATORY)
+Enter code in caps</v>
       </c>
       <c r="D26" t="str">
-        <v>Upload clear photo of team member 4 pose.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
       <c r="E26" t="str">
         <v>yes</v>
       </c>
-    </row>
-    <row r="27" xml:space="preserve">
+      <c r="F26" t="str">
+        <v>❌ Volunteer completion code is mandatory.</v>
+      </c>
+      <c r="G26" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'MECH-PS-1'</v>
+      </c>
+      <c r="H26" t="str">
+        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="str">
-        <v>text</v>
-      </c>
-      <c r="B27" t="str">
-        <v>r2_var1_volunteer_code</v>
-      </c>
-      <c r="C27" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Verification Code
-Enter code in caps</v>
-      </c>
-      <c r="D27" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E27" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F27" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH-PS-1'</v>
-      </c>
-      <c r="G27" t="str">
-        <v>❌ Incorrect code. Enter the code in CAPS provided by the volunteer.</v>
+        <v>end_group</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>begin_group</v>
+      </c>
+      <c r="B28" t="str">
+        <v>r2_var_b_group</v>
+      </c>
+      <c r="C28" t="str">
+        <v>VARIANT B — PAPER BALL</v>
+      </c>
+      <c r="I28" t="str">
+        <v>${r2_variant_selected} = 'var_b'</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
       <c r="A29" t="str">
-        <v>begin_group</v>
+        <v>note</v>
       </c>
       <c r="B29" t="str">
-        <v>r2_var2_group</v>
-      </c>
-      <c r="C29" t="str">
-        <v>VARIANT 2 — PAPER BALL</v>
-      </c>
-      <c r="H29" t="str">
-        <v>${r2_chit_selected} = 'var2'</v>
+        <v>r2_var_b_paperball_note</v>
+      </c>
+      <c r="C29" t="str" xml:space="preserve">
+        <v xml:space="preserve">🎾 VARIANT B: PAPER BALL
+Instructions:
+1. Refer to the challenge explained by the volunteer.
+2. Complete the challenge with the volunteer.
+3. Enter the challenge completion code provided by the volunteer.
+Enter code in caps</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Complete paper ball challenge as explained by volunteer.</v>
       </c>
     </row>
     <row r="30" xml:space="preserve">
       <c r="A30" t="str">
-        <v>note</v>
+        <v>text</v>
       </c>
       <c r="B30" t="str">
-        <v>r2_var2_paperball_note</v>
+        <v>r2_var_b_volunteer_code</v>
       </c>
       <c r="C30" t="str" xml:space="preserve">
-        <v xml:space="preserve">🎾 MINI-CHALLENGE: PAPER BALL
-Challenge: Complete the paper ball &amp; exam pads coordination challenge.
-Instructions:
-1. Use exam pads to bounce / guide the paper ball into the target container.
-2. Complete challenge with volunteer verification.
-3. Enter clearance code provided by volunteer.
+        <v xml:space="preserve">Enter Challenge Completion Code from Volunteer (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D30" t="str">
-        <v>Complete paper ball challenge with volunteer.</v>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E30" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F30" t="str">
+        <v>❌ Volunteer completion code is mandatory.</v>
+      </c>
+      <c r="G30" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'ME-PB-1'</v>
+      </c>
+      <c r="H30" t="str">
+        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="str">
-        <v>text</v>
-      </c>
-      <c r="B31" t="str">
-        <v>r2_var2_volunteer_code</v>
-      </c>
-      <c r="C31" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Verification Code
-Enter code in caps</v>
-      </c>
-      <c r="D31" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E31" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F31" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ME-PB-1'</v>
-      </c>
-      <c r="G31" t="str">
-        <v>❌ Incorrect code. Enter the code in CAPS provided by the volunteer.</v>
+        <v>end_group</v>
       </c>
     </row>
     <row r="32">
@@ -954,33 +1005,28 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>begin_group</v>
+      </c>
+      <c r="B33" t="str">
+        <v>r3_loc_group</v>
+      </c>
+      <c r="C33" t="str">
+        <v>ROUND 3</v>
+      </c>
+      <c r="I33" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1')</v>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
       <c r="A34" t="str">
-        <v>begin_group</v>
+        <v>note</v>
       </c>
       <c r="B34" t="str">
-        <v>r3_loc_group</v>
-      </c>
-      <c r="C34" t="str">
-        <v>ROUND 3 LOCATION CLUE</v>
-      </c>
-      <c r="H34" t="str">
-        <v>(translate(normalize-space(${r2_var1_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH-PS-1' or translate(normalize-space(${r2_var2_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ME-PB-1')</v>
-      </c>
-    </row>
-    <row r="35" xml:space="preserve">
-      <c r="A35" t="str">
-        <v>note</v>
-      </c>
-      <c r="B35" t="str">
-        <v>r3_shuffled_numbers_note</v>
-      </c>
-      <c r="C35" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 3 LOCATION CLUE: SHUFFLED NUMBERS
-Arrange and decode the shuffled numbers using the example word key to decode the next destination!
+        <v>r3_cipher_examples_note</v>
+      </c>
+      <c r="C34" t="str" xml:space="preserve">
+        <v xml:space="preserve">📍 ROUND 3
+Decode each number code using the cipher system to discover clue words!
 🔢 CIPHER KEY: Q=20, U=24, I=12, Z=29
 Verification Examples:
 • CROWD = 6-21-18-26-7
@@ -988,8 +1034,35 @@
 • STEEL BOX = 22-23-8-8-15 / 5-18-27
 Enter code in caps</v>
       </c>
+      <c r="D34" t="str">
+        <v>Decode each number code.</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>text</v>
+      </c>
+      <c r="B35" t="str">
+        <v>r3_decode_w1</v>
+      </c>
+      <c r="C35" t="str" xml:space="preserve">
+        <v xml:space="preserve">Decode Number Code 1: [ 11-4-15-7-12-21-4-16 ] (MANDATORY)
+Enter code in caps</v>
+      </c>
       <c r="D35" t="str">
-        <v>Decode each number code.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E35" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F35" t="str">
+        <v>❌ Decoding word 1 is mandatory.</v>
+      </c>
+      <c r="G35" t="str">
+        <v>regex(., '^[A-Z]+$') and normalize-space(.) = 'HALDIRAM'</v>
+      </c>
+      <c r="H35" t="str">
+        <v>❌ Incorrect word. Enter the decoded word in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="36" xml:space="preserve">
@@ -997,10 +1070,10 @@
         <v>text</v>
       </c>
       <c r="B36" t="str">
-        <v>r3_decode_w1</v>
+        <v>r3_decode_w2</v>
       </c>
       <c r="C36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Decode Number Code 1: [ 11-4-15-7-12-21-4-16 ]
+        <v xml:space="preserve">Decode Number Code 2: [ 5-21-4-10-14 ] (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D36" t="str">
@@ -1010,10 +1083,13 @@
         <v>yes</v>
       </c>
       <c r="F36" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HALDIRAM'</v>
+        <v>❌ Decoding word 2 is mandatory.</v>
       </c>
       <c r="G36" t="str">
-        <v>❌ Incorrect word. Please decode the number sequence.</v>
+        <v>regex(., '^[A-Z]+$') and normalize-space(.) = 'BREAK'</v>
+      </c>
+      <c r="H36" t="str">
+        <v>❌ Incorrect word. Enter the decoded word in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="37" xml:space="preserve">
@@ -1021,10 +1097,10 @@
         <v>text</v>
       </c>
       <c r="B37" t="str">
-        <v>r3_decode_w2</v>
+        <v>r3_decode_w3</v>
       </c>
       <c r="C37" t="str" xml:space="preserve">
-        <v xml:space="preserve">Decode Number Code 2: [ 5-21-4-10-14 ]
+        <v xml:space="preserve">Decode Number Code 3: [ 5-18-23-23-15-8 ] (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D37" t="str">
@@ -1034,10 +1110,13 @@
         <v>yes</v>
       </c>
       <c r="F37" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BREAK'</v>
+        <v>❌ Decoding word 3 is mandatory.</v>
       </c>
       <c r="G37" t="str">
-        <v>❌ Incorrect word. Please decode the number sequence.</v>
+        <v>regex(., '^[A-Z]+$') and normalize-space(.) = 'BOTTLE'</v>
+      </c>
+      <c r="H37" t="str">
+        <v>❌ Incorrect word. Enter the decoded word in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="38" xml:space="preserve">
@@ -1045,10 +1124,10 @@
         <v>text</v>
       </c>
       <c r="B38" t="str">
-        <v>r3_decode_w3</v>
+        <v>r3_decode_w4</v>
       </c>
       <c r="C38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Decode Number Code 3: [ 5-18-23-23-15-8 ]
+        <v xml:space="preserve">Decode Number Code 4: [ 20-24-8-24-8 ] (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D38" t="str">
@@ -1058,10 +1137,13 @@
         <v>yes</v>
       </c>
       <c r="F38" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BOTTLE'</v>
+        <v>❌ Decoding word 4 is mandatory.</v>
       </c>
       <c r="G38" t="str">
-        <v>❌ Incorrect word. Please decode the number sequence.</v>
+        <v>regex(., '^[A-Z]+$') and normalize-space(.) = 'QUEUE'</v>
+      </c>
+      <c r="H38" t="str">
+        <v>❌ Incorrect word. Enter the decoded word in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="39" xml:space="preserve">
@@ -1069,10 +1151,10 @@
         <v>text</v>
       </c>
       <c r="B39" t="str">
-        <v>r3_decode_w4</v>
+        <v>r3_decode_w5</v>
       </c>
       <c r="C39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Decode Number Code 4: [ 20-24-8-24-8 ]
+        <v xml:space="preserve">Decode Number Code 5: [ 6-18-24-17-23-8-21 ] (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D39" t="str">
@@ -1082,10 +1164,13 @@
         <v>yes</v>
       </c>
       <c r="F39" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'QUEUE'</v>
+        <v>❌ Decoding word 5 is mandatory.</v>
       </c>
       <c r="G39" t="str">
-        <v>❌ Incorrect word. Please decode the number sequence.</v>
+        <v>regex(., '^[A-Z]+$') and normalize-space(.) = 'COUNTER'</v>
+      </c>
+      <c r="H39" t="str">
+        <v>❌ Incorrect word. Enter the decoded word in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="40" xml:space="preserve">
@@ -1093,10 +1178,16 @@
         <v>text</v>
       </c>
       <c r="B40" t="str">
-        <v>r3_decode_w5</v>
+        <v>r3_destination_guess</v>
       </c>
       <c r="C40" t="str" xml:space="preserve">
-        <v xml:space="preserve">Decode Number Code 5: [ 6-18-24-17-23-8-21 ]
+        <v xml:space="preserve">Decoded Clues:
+1. ${r3_decode_w1}
+2. ${r3_decode_w2}
+3. ${r3_decode_w3}
+4. ${r3_decode_w4}
+5. ${r3_decode_w5}
+Based on all your decoded clue words, guess and enter the destination campus block: (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D40" t="str">
@@ -1106,86 +1197,90 @@
         <v>yes</v>
       </c>
       <c r="F40" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'COUNTER'</v>
+        <v>❌ Guessing the destination campus block is mandatory.</v>
       </c>
       <c r="G40" t="str">
-        <v>❌ Incorrect word. Please decode the number sequence.</v>
-      </c>
-    </row>
-    <row r="41" xml:space="preserve">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'FOOD COURT' or normalize-space(.) = 'FOOD CANTEEN' or normalize-space(.) = 'CANTEEN' or normalize-space(.) = 'FOODCOURT' or normalize-space(.) = 'NEW CANTEEN')</v>
+      </c>
+      <c r="H40" t="str">
+        <v>❌ Incorrect destination. Review your decoded clues and enter the destination in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="I40" t="str">
+        <v>(normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER')</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" t="str">
-        <v>text</v>
-      </c>
-      <c r="B41" t="str">
-        <v>r3_destination_guess</v>
-      </c>
-      <c r="C41" t="str" xml:space="preserve">
-        <v xml:space="preserve">Where do these decoded clues lead your team to?
-Enter code in caps</v>
-      </c>
-      <c r="D41" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E41" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F41" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOOD COURT' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOODCOURT' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEW CANTEEN'</v>
-      </c>
-      <c r="G41" t="str">
-        <v>❌ Incorrect destination. Enter the destination in CAPS.</v>
-      </c>
-      <c r="H41" t="str">
-        <v>(translate(normalize-space(${r3_decode_w1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HALDIRAM' and translate(normalize-space(${r3_decode_w2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BREAK' and translate(normalize-space(${r3_decode_w3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BOTTLE' and translate(normalize-space(${r3_decode_w4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'QUEUE' and translate(normalize-space(${r3_decode_w5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'COUNTER')</v>
+        <v>end_group</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>begin_group</v>
+      </c>
+      <c r="B42" t="str">
+        <v>r3_qr_group</v>
+      </c>
+      <c r="C42" t="str">
+        <v>ROUND 3 — QR HUNT</v>
+      </c>
+      <c r="I42" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1') and (normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER') and (normalize-space(${r3_destination_guess}) = 'FOOD COURT' or normalize-space(${r3_destination_guess}) = 'FOOD CANTEEN' or normalize-space(${r3_destination_guess}) = 'CANTEEN' or normalize-space(${r3_destination_guess}) = 'FOODCOURT' or normalize-space(${r3_destination_guess}) = 'NEW CANTEEN')</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
       <c r="A43" t="str">
-        <v>begin_group</v>
+        <v>note</v>
       </c>
       <c r="B43" t="str">
-        <v>r3_qr_group</v>
-      </c>
-      <c r="C43" t="str">
-        <v>ROUND 3 — QR HUNT</v>
-      </c>
-      <c r="H43" t="str">
-        <v>(translate(normalize-space(${r2_var1_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH-PS-1' or translate(normalize-space(${r2_var2_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ME-PB-1') and (translate(normalize-space(${r3_decode_w1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HALDIRAM' and translate(normalize-space(${r3_decode_w2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BREAK' and translate(normalize-space(${r3_decode_w3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BOTTLE' and translate(normalize-space(${r3_decode_w4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'QUEUE' and translate(normalize-space(${r3_decode_w5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'COUNTER') and (translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOOD COURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOODCOURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEW CANTEEN')</v>
-      </c>
-    </row>
-    <row r="44" xml:space="preserve">
+        <v>r3_fc_hunt_intro</v>
+      </c>
+      <c r="C43" t="str" xml:space="preserve">
+        <v xml:space="preserve">📍 ROUND 3: QR HUNT
+Proceed to the destination block!
+Search around the area and scan QR codes to find the correct one in a fun way! Once found, scan it below and then ask the volunteer with a LUMINUS ID card for your completion code.
+Enter code in caps</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Scan QR codes in the area to find the correct one.</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" t="str">
-        <v>note</v>
+        <v>barcode</v>
       </c>
       <c r="B44" t="str">
-        <v>r3_fc_hunt_intro</v>
-      </c>
-      <c r="C44" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 3: QR HUNT
-Search around the location to find and scan the hidden QR code!
-Instructions:
-1. Search the area to locate the hidden QR code.
-2. Scan the QR code using the in-app scanner below.
-Enter code in caps</v>
+        <v>r3_qr_scan</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Scan Discovered QR Code (MANDATORY)</v>
       </c>
       <c r="D44" t="str">
-        <v>Find and scan the QR code.</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>Scan the correct hidden QR code.</v>
+      </c>
+      <c r="E44" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F44" t="str">
+        <v>❌ Scanning the discovered QR code is mandatory.</v>
+      </c>
+      <c r="G44" t="str">
+        <v>normalize-space(.) = 'FAKE-ME-CYBER'</v>
+      </c>
+      <c r="H44" t="str">
+        <v>❌ Incorrect QR code scanned. Keep searching the area for the correct QR code.</v>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
       <c r="A45" t="str">
-        <v>barcode</v>
+        <v>text</v>
       </c>
       <c r="B45" t="str">
-        <v>r3_qr_scan</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Scan Discovered QR Code</v>
+        <v>r3_qr_volunteer_code</v>
+      </c>
+      <c r="C45" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Volunteer Completion Code (MANDATORY)
+Enter code in caps</v>
       </c>
       <c r="D45" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
@@ -1194,10 +1289,16 @@
         <v>yes</v>
       </c>
       <c r="F45" t="str">
-        <v>normalize-space(.) = 'FAKE-ME-CYBER' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FAKE-ME-CYBER'</v>
+        <v>❌ Volunteer completion code is mandatory.</v>
       </c>
       <c r="G45" t="str">
-        <v>❌ Incorrect QR code scanned. Locate and scan the correct QR code.</v>
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'QR-HUNT-GOOD'</v>
+      </c>
+      <c r="H45" t="str">
+        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer with a LUMINUS ID card.</v>
+      </c>
+      <c r="I45" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1') and (normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER') and (normalize-space(${r3_destination_guess}) = 'FOOD COURT' or normalize-space(${r3_destination_guess}) = 'FOOD CANTEEN' or normalize-space(${r3_destination_guess}) = 'CANTEEN' or normalize-space(${r3_destination_guess}) = 'FOODCOURT' or normalize-space(${r3_destination_guess}) = 'NEW CANTEEN') and normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER'</v>
       </c>
     </row>
     <row r="46">
@@ -1215,8 +1316,8 @@
       <c r="C47" t="str">
         <v>ROUND 4 LOCATION CLUE</v>
       </c>
-      <c r="H47" t="str">
-        <v>(translate(normalize-space(${r2_var1_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH-PS-1' or translate(normalize-space(${r2_var2_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ME-PB-1') and (translate(normalize-space(${r3_decode_w1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HALDIRAM' and translate(normalize-space(${r3_decode_w2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BREAK' and translate(normalize-space(${r3_decode_w3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BOTTLE' and translate(normalize-space(${r3_decode_w4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'QUEUE' and translate(normalize-space(${r3_decode_w5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'COUNTER') and (translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOOD COURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOODCOURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEW CANTEEN') and (normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' or translate(normalize-space(${r3_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FAKE-ME-CYBER')</v>
+      <c r="I47" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1') and (normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER') and (normalize-space(${r3_destination_guess}) = 'FOOD COURT' or normalize-space(${r3_destination_guess}) = 'FOOD CANTEEN' or normalize-space(${r3_destination_guess}) = 'CANTEEN' or normalize-space(${r3_destination_guess}) = 'FOODCOURT' or normalize-space(${r3_destination_guess}) = 'NEW CANTEEN') and normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' and normalize-space(${r3_qr_volunteer_code}) = 'QR-HUNT-GOOD'</v>
       </c>
     </row>
     <row r="48" xml:space="preserve">
@@ -1250,7 +1351,7 @@
         <v>r4_caesar_decoded_answer</v>
       </c>
       <c r="C49" t="str" xml:space="preserve">
-        <v xml:space="preserve">Decode Encrypted Message [ HDGJW ]:
+        <v xml:space="preserve">Decode Encrypted Message [ HDGJW ]: (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D49" t="str">
@@ -1260,10 +1361,13 @@
         <v>yes</v>
       </c>
       <c r="F49" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY SEMINAR HALL' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER SEMINAR HALL'</v>
+        <v>❌ Decoding the message is mandatory.</v>
       </c>
       <c r="G49" t="str">
-        <v>❌ Incorrect destination. Decode the encrypted message by shifting each letter 5 steps backward.</v>
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'CYBER' or normalize-space(.) = 'CYBER SECURITY' or normalize-space(.) = 'CY' or normalize-space(.) = 'CY SEMINAR HALL' or normalize-space(.) = 'CYBER SEMINAR HALL')</v>
+      </c>
+      <c r="H49" t="str">
+        <v>❌ Incorrect destination. Decode the encrypted message by shifting each letter 5 steps backward in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="50">
@@ -1281,8 +1385,8 @@
       <c r="C51" t="str">
         <v>ROUND 4 — PHYSICAL CHALLENGE</v>
       </c>
-      <c r="H51" t="str">
-        <v>(translate(normalize-space(${r2_var1_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH-PS-1' or translate(normalize-space(${r2_var2_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ME-PB-1') and (translate(normalize-space(${r3_decode_w1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HALDIRAM' and translate(normalize-space(${r3_decode_w2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BREAK' and translate(normalize-space(${r3_decode_w3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BOTTLE' and translate(normalize-space(${r3_decode_w4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'QUEUE' and translate(normalize-space(${r3_decode_w5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'COUNTER') and (translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOOD COURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOODCOURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEW CANTEEN') and (normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' or translate(normalize-space(${r3_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FAKE-ME-CYBER') and (translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY SEMINAR HALL' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER SEMINAR HALL')</v>
+      <c r="I51" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1') and (normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER') and (normalize-space(${r3_destination_guess}) = 'FOOD COURT' or normalize-space(${r3_destination_guess}) = 'FOOD CANTEEN' or normalize-space(${r3_destination_guess}) = 'CANTEEN' or normalize-space(${r3_destination_guess}) = 'FOODCOURT' or normalize-space(${r3_destination_guess}) = 'NEW CANTEEN') and normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' and normalize-space(${r3_qr_volunteer_code}) = 'QR-HUNT-GOOD' and (normalize-space(${r4_caesar_decoded_answer}) = 'CYBER' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SECURITY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY SEMINAR HALL' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SEMINAR HALL')</v>
       </c>
     </row>
     <row r="52" xml:space="preserve">
@@ -1294,15 +1398,12 @@
       </c>
       <c r="C52" t="str" xml:space="preserve">
         <v xml:space="preserve">📍 ROUND 4: PHYSICAL CHALLENGE
-Report immediately to the CY Seminar Hall!
-Instructions:
-1. Meet the volunteers at CY Seminar Hall.
-2. Successfully complete the physical agility &amp; coordination challenge.
-3. Receive clearance code from the volunteer.
+Proceed to the block you answered!
+Navigate the hall in that block, meet the volunteers, and ask them for the start code.
 Enter code in caps</v>
       </c>
       <c r="D52" t="str">
-        <v>Complete physical challenge at CY Seminar Hall.</v>
+        <v>Go to the seminar hall and ask volunteer for start code.</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
@@ -1310,132 +1411,143 @@
         <v>text</v>
       </c>
       <c r="B53" t="str">
+        <v>r4_start_code</v>
+      </c>
+      <c r="C53" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Challenge Start Code from Volunteer (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D53" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E53" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F53" t="str">
+        <v>❌ Challenge start code is mandatory.</v>
+      </c>
+      <c r="G53" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'START-PHY'</v>
+      </c>
+      <c r="H53" t="str">
+        <v>❌ Incorrect start code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="A54" t="str">
+        <v>note</v>
+      </c>
+      <c r="B54" t="str">
+        <v>r4_perform_phy_note</v>
+      </c>
+      <c r="C54" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏃 PERFORM PHYSICAL CHALLENGE
+Perform the physical agility &amp; coordination challenge as instructed by the volunteers in the hall. Once completed, collect the finish code from the volunteer.
+Enter code in caps</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Complete physical challenge with volunteer.</v>
+      </c>
+      <c r="I54" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1') and (normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER') and (normalize-space(${r3_destination_guess}) = 'FOOD COURT' or normalize-space(${r3_destination_guess}) = 'FOOD CANTEEN' or normalize-space(${r3_destination_guess}) = 'CANTEEN' or normalize-space(${r3_destination_guess}) = 'FOODCOURT' or normalize-space(${r3_destination_guess}) = 'NEW CANTEEN') and normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' and normalize-space(${r3_qr_volunteer_code}) = 'QR-HUNT-GOOD' and (normalize-space(${r4_caesar_decoded_answer}) = 'CYBER' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SECURITY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY SEMINAR HALL' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SEMINAR HALL') and normalize-space(${r4_start_code}) = 'START-PHY'</v>
+      </c>
+    </row>
+    <row r="55" xml:space="preserve">
+      <c r="A55" t="str">
+        <v>text</v>
+      </c>
+      <c r="B55" t="str">
         <v>r4_cy_volunteer_code</v>
       </c>
-      <c r="C53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Verification Code
-Enter code in caps</v>
-      </c>
-      <c r="D53" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E53" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F53" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PHY-CY'</v>
-      </c>
-      <c r="G53" t="str">
-        <v>❌ Incorrect code. Enter the code in CAPS provided by the volunteer.</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
+      <c r="C55" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Challenge Finish Code from Volunteer (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D55" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E55" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F55" t="str">
+        <v>❌ Challenge finish code is mandatory.</v>
+      </c>
+      <c r="G55" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'PHY-CY'</v>
+      </c>
+      <c r="H55" t="str">
+        <v>❌ Incorrect finish code. Enter the finish code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+      <c r="I55" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1') and (normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER') and (normalize-space(${r3_destination_guess}) = 'FOOD COURT' or normalize-space(${r3_destination_guess}) = 'FOOD CANTEEN' or normalize-space(${r3_destination_guess}) = 'CANTEEN' or normalize-space(${r3_destination_guess}) = 'FOODCOURT' or normalize-space(${r3_destination_guess}) = 'NEW CANTEEN') and normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' and normalize-space(${r3_qr_volunteer_code}) = 'QR-HUNT-GOOD' and (normalize-space(${r4_caesar_decoded_answer}) = 'CYBER' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SECURITY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY SEMINAR HALL' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SEMINAR HALL') and normalize-space(${r4_start_code}) = 'START-PHY'</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
         <v>end_group</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="str">
+    <row r="57">
+      <c r="A57" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B55" t="str">
+      <c r="B57" t="str">
         <v>final_puzzles_group</v>
       </c>
-      <c r="C55" t="str">
-        <v>FINAL PUZZLES</v>
-      </c>
-      <c r="H55" t="str">
-        <v>(translate(normalize-space(${r2_var1_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH-PS-1' or translate(normalize-space(${r2_var2_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ME-PB-1') and (translate(normalize-space(${r3_decode_w1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HALDIRAM' and translate(normalize-space(${r3_decode_w2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BREAK' and translate(normalize-space(${r3_decode_w3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BOTTLE' and translate(normalize-space(${r3_decode_w4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'QUEUE' and translate(normalize-space(${r3_decode_w5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'COUNTER') and (translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOOD COURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOODCOURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEW CANTEEN') and (normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' or translate(normalize-space(${r3_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FAKE-ME-CYBER') and (translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY SEMINAR HALL' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER SEMINAR HALL') and translate(normalize-space(${r4_cy_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PHY-CY'</v>
-      </c>
-    </row>
-    <row r="56" xml:space="preserve">
-      <c r="A56" t="str">
-        <v>note</v>
-      </c>
-      <c r="B56" t="str">
-        <v>final_audi_stage_intro</v>
-      </c>
-      <c r="C56" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏛️ FINAL CHALLENGES
-Proceed to the location and solve the two final riddles!
-Enter code in caps</v>
-      </c>
-      <c r="D56" t="str">
-        <v>Solve the final riddles.</v>
-      </c>
-    </row>
-    <row r="57" xml:space="preserve">
-      <c r="A57" t="str">
-        <v>text</v>
-      </c>
-      <c r="B57" t="str">
-        <v>final_riddle1_answer</v>
-      </c>
-      <c r="C57" t="str" xml:space="preserve">
-        <v xml:space="preserve">🧩 RIDDLE 1:
-"I am a place of darkness until the lights ignite. I hold hundreds of red seats, host grand orientations, and echo with voices through microphones. Where are you standing?"
-Enter code in caps</v>
-      </c>
-      <c r="D57" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E57" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F57" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI'</v>
-      </c>
-      <c r="G57" t="str">
-        <v>❌ Incorrect answer. Solve the riddle and enter in CAPS.</v>
+      <c r="C57" t="str">
+        <v>FINAL ROUND</v>
+      </c>
+      <c r="I57" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1') and (normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER') and (normalize-space(${r3_destination_guess}) = 'FOOD COURT' or normalize-space(${r3_destination_guess}) = 'FOOD CANTEEN' or normalize-space(${r3_destination_guess}) = 'CANTEEN' or normalize-space(${r3_destination_guess}) = 'FOODCOURT' or normalize-space(${r3_destination_guess}) = 'NEW CANTEEN') and normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' and normalize-space(${r3_qr_volunteer_code}) = 'QR-HUNT-GOOD' and (normalize-space(${r4_caesar_decoded_answer}) = 'CYBER' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SECURITY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY SEMINAR HALL' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SEMINAR HALL') and normalize-space(${r4_start_code}) = 'START-PHY' and normalize-space(${r4_cy_volunteer_code}) = 'PHY-CY'</v>
       </c>
     </row>
     <row r="58" xml:space="preserve">
       <c r="A58" t="str">
-        <v>text</v>
+        <v>note</v>
       </c>
       <c r="B58" t="str">
-        <v>final_riddle2_stage_answer</v>
+        <v>final_audi_stage_intro</v>
       </c>
       <c r="C58" t="str" xml:space="preserve">
-        <v xml:space="preserve">🎭 RIDDLE 2:
-"I am elevated above the crowd, where performers stand and spotlights shine. Underneath my wooden floor or behind the curtains, the ultimate secret waits. What am I?"
+        <v xml:space="preserve">🏛️ FINAL ROUND — RIDDLES
+Solve the two final riddles to reveal the ultimate stage!
 Enter code in caps</v>
       </c>
       <c r="D58" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E58" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F58" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE'</v>
-      </c>
-      <c r="G58" t="str">
-        <v>❌ Incorrect answer. Solve the stage riddle and enter in CAPS.</v>
-      </c>
-      <c r="H58" t="str">
-        <v>(translate(normalize-space(${r2_var1_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH-PS-1' or translate(normalize-space(${r2_var2_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ME-PB-1') and (translate(normalize-space(${r3_decode_w1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HALDIRAM' and translate(normalize-space(${r3_decode_w2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BREAK' and translate(normalize-space(${r3_decode_w3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BOTTLE' and translate(normalize-space(${r3_decode_w4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'QUEUE' and translate(normalize-space(${r3_decode_w5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'COUNTER') and (translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOOD COURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOODCOURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEW CANTEEN') and (normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' or translate(normalize-space(${r3_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FAKE-ME-CYBER') and (translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY SEMINAR HALL' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER SEMINAR HALL') and translate(normalize-space(${r4_cy_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PHY-CY' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI')</v>
+        <v>Solve the final riddles.</v>
       </c>
     </row>
     <row r="59" xml:space="preserve">
       <c r="A59" t="str">
-        <v>image</v>
+        <v>text</v>
       </c>
       <c r="B59" t="str">
-        <v>final_solved_puzzle_photo</v>
+        <v>final_riddle1_answer</v>
       </c>
       <c r="C59" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Your Solved Puzzle
-Photo upload is mandatory</v>
+        <v xml:space="preserve">🧩 AUDITORIUM RIDDLE: (MANDATORY)
+"I am empty, yet I am built for crowds.
+I have a stage, but no actors of my own.
+I have countless seats, but none are meant to sleep.
+When a voice rises before me, silence falls behind me.
+When the lights awaken, all eyes face one direction.
+What am I?"
+Enter code in caps</v>
       </c>
       <c r="D59" t="str">
-        <v>Take a clear photo of your team's completed/solved puzzle.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
       <c r="E59" t="str">
         <v>yes</v>
       </c>
+      <c r="F59" t="str">
+        <v>❌ Solving Riddle 1 is mandatory.</v>
+      </c>
+      <c r="G59" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'AUDITORIUM' or normalize-space(.) = 'AUDI')</v>
+      </c>
       <c r="H59" t="str">
-        <v>(translate(normalize-space(${r2_var1_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH-PS-1' or translate(normalize-space(${r2_var2_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ME-PB-1') and (translate(normalize-space(${r3_decode_w1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HALDIRAM' and translate(normalize-space(${r3_decode_w2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BREAK' and translate(normalize-space(${r3_decode_w3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BOTTLE' and translate(normalize-space(${r3_decode_w4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'QUEUE' and translate(normalize-space(${r3_decode_w5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'COUNTER') and (translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOOD COURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOODCOURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEW CANTEEN') and (normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' or translate(normalize-space(${r3_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FAKE-ME-CYBER') and (translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY SEMINAR HALL' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER SEMINAR HALL') and translate(normalize-space(${r4_cy_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PHY-CY' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI') and translate(normalize-space(${final_riddle2_stage_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE'</v>
+        <v>❌ Incorrect answer. Solve Riddle 1 and enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="60" xml:space="preserve">
@@ -1443,10 +1555,11 @@
         <v>text</v>
       </c>
       <c r="B60" t="str">
-        <v>final_stage_volunteer_code</v>
+        <v>final_riddle2_stage_answer</v>
       </c>
       <c r="C60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Final Volunteer Clearance Code
+        <v xml:space="preserve">🎭 RIDDLE 2: (MANDATORY)
+"I am elevated above the crowd, where performers stand and spotlights shine. Underneath my wooden floor or behind the curtains, the ultimate secret waits. What am I?"
 Enter code in caps</v>
       </c>
       <c r="D60" t="str">
@@ -1456,13 +1569,16 @@
         <v>yes</v>
       </c>
       <c r="F60" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH1'</v>
+        <v>❌ Solving Riddle 2 is mandatory.</v>
       </c>
       <c r="G60" t="str">
-        <v>❌ Incorrect code. Enter the code in CAPS provided by the Chief Judge.</v>
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'STAGE'</v>
       </c>
       <c r="H60" t="str">
-        <v>(translate(normalize-space(${r2_var1_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH-PS-1' or translate(normalize-space(${r2_var2_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ME-PB-1') and (translate(normalize-space(${r3_decode_w1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HALDIRAM' and translate(normalize-space(${r3_decode_w2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BREAK' and translate(normalize-space(${r3_decode_w3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BOTTLE' and translate(normalize-space(${r3_decode_w4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'QUEUE' and translate(normalize-space(${r3_decode_w5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'COUNTER') and (translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOOD COURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOODCOURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEW CANTEEN') and (normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' or translate(normalize-space(${r3_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FAKE-ME-CYBER') and (translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY SEMINAR HALL' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER SEMINAR HALL') and translate(normalize-space(${r4_cy_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PHY-CY' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI') and translate(normalize-space(${final_riddle2_stage_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE'</v>
+        <v>❌ Incorrect answer. Solve Riddle 2 and enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="I60" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1') and (normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER') and (normalize-space(${r3_destination_guess}) = 'FOOD COURT' or normalize-space(${r3_destination_guess}) = 'FOOD CANTEEN' or normalize-space(${r3_destination_guess}) = 'CANTEEN' or normalize-space(${r3_destination_guess}) = 'FOODCOURT' or normalize-space(${r3_destination_guess}) = 'NEW CANTEEN') and normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' and normalize-space(${r3_qr_volunteer_code}) = 'QR-HUNT-GOOD' and (normalize-space(${r4_caesar_decoded_answer}) = 'CYBER' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SECURITY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY SEMINAR HALL' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SEMINAR HALL') and normalize-space(${r4_start_code}) = 'START-PHY' and normalize-space(${r4_cy_volunteer_code}) = 'PHY-CY' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI')</v>
       </c>
     </row>
     <row r="61" xml:space="preserve">
@@ -1470,28 +1586,102 @@
         <v>note</v>
       </c>
       <c r="B61" t="str">
+        <v>final_tied_note</v>
+      </c>
+      <c r="C61" t="str" xml:space="preserve">
+        <v xml:space="preserve">⚠️ GRAND FINALE RUSH!
+Go to the guessed block with your legs and hands tied (as coordinated by volunteers)!
+Once you reach, solve the final puzzle at the stage!
+Enter code in caps</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Proceed with hands and legs tied as instructed by volunteers.</v>
+      </c>
+      <c r="I61" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1') and (normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER') and (normalize-space(${r3_destination_guess}) = 'FOOD COURT' or normalize-space(${r3_destination_guess}) = 'FOOD CANTEEN' or normalize-space(${r3_destination_guess}) = 'CANTEEN' or normalize-space(${r3_destination_guess}) = 'FOODCOURT' or normalize-space(${r3_destination_guess}) = 'NEW CANTEEN') and normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' and normalize-space(${r3_qr_volunteer_code}) = 'QR-HUNT-GOOD' and (normalize-space(${r4_caesar_decoded_answer}) = 'CYBER' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SECURITY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY SEMINAR HALL' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SEMINAR HALL') and normalize-space(${r4_start_code}) = 'START-PHY' and normalize-space(${r4_cy_volunteer_code}) = 'PHY-CY' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str">
+        <v>image</v>
+      </c>
+      <c r="B62" t="str">
+        <v>final_solved_puzzle_photo</v>
+      </c>
+      <c r="C62" t="str" xml:space="preserve">
+        <v xml:space="preserve">📸 Upload Photo of Your Solved Puzzle (MANDATORY)
+Photo upload is mandatory</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Take a clear photo of your team's completed/solved puzzle.</v>
+      </c>
+      <c r="E62" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F62" t="str">
+        <v>❌ Uploading photo of the solved puzzle is mandatory.</v>
+      </c>
+      <c r="I62" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1') and (normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER') and (normalize-space(${r3_destination_guess}) = 'FOOD COURT' or normalize-space(${r3_destination_guess}) = 'FOOD CANTEEN' or normalize-space(${r3_destination_guess}) = 'CANTEEN' or normalize-space(${r3_destination_guess}) = 'FOODCOURT' or normalize-space(${r3_destination_guess}) = 'NEW CANTEEN') and normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' and normalize-space(${r3_qr_volunteer_code}) = 'QR-HUNT-GOOD' and (normalize-space(${r4_caesar_decoded_answer}) = 'CYBER' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SECURITY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY SEMINAR HALL' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SEMINAR HALL') and normalize-space(${r4_start_code}) = 'START-PHY' and normalize-space(${r4_cy_volunteer_code}) = 'PHY-CY' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="63" xml:space="preserve">
+      <c r="A63" t="str">
+        <v>text</v>
+      </c>
+      <c r="B63" t="str">
+        <v>final_stage_volunteer_code</v>
+      </c>
+      <c r="C63" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Final Volunteer Clearance Code (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D63" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E63" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F63" t="str">
+        <v>❌ Final clearance code is mandatory.</v>
+      </c>
+      <c r="G63" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'FINAL-PATH1'</v>
+      </c>
+      <c r="H63" t="str">
+        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the Chief Judge.</v>
+      </c>
+      <c r="I63" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1') and (normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER') and (normalize-space(${r3_destination_guess}) = 'FOOD COURT' or normalize-space(${r3_destination_guess}) = 'FOOD CANTEEN' or normalize-space(${r3_destination_guess}) = 'CANTEEN' or normalize-space(${r3_destination_guess}) = 'FOODCOURT' or normalize-space(${r3_destination_guess}) = 'NEW CANTEEN') and normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' and normalize-space(${r3_qr_volunteer_code}) = 'QR-HUNT-GOOD' and (normalize-space(${r4_caesar_decoded_answer}) = 'CYBER' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SECURITY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY SEMINAR HALL' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SEMINAR HALL') and normalize-space(${r4_start_code}) = 'START-PHY' and normalize-space(${r4_cy_volunteer_code}) = 'PHY-CY' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64" t="str">
+        <v>note</v>
+      </c>
+      <c r="B64" t="str">
         <v>final_congratulations_screen</v>
       </c>
-      <c r="C61" t="str" xml:space="preserve">
+      <c r="C64" t="str" xml:space="preserve">
         <v xml:space="preserve">🎉 CONGRATULATIONS! YOU HAVE COMPLETED PATH 1!
-🏆 You have successfully conquered every challenge, puzzle, and cipher on PATH 1!
-Show this completion screen immediately to the Chief Judge to lock in your finishing timestamp and rank!</v>
-      </c>
-      <c r="D61" t="str">
-        <v>Report to Chief Judge to finalize completion.</v>
-      </c>
-      <c r="H61" t="str">
-        <v>(translate(normalize-space(${r2_var1_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MECH-PS-1' or translate(normalize-space(${r2_var2_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ME-PB-1') and (translate(normalize-space(${r3_decode_w1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HALDIRAM' and translate(normalize-space(${r3_decode_w2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BREAK' and translate(normalize-space(${r3_decode_w3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BOTTLE' and translate(normalize-space(${r3_decode_w4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'QUEUE' and translate(normalize-space(${r3_decode_w5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'COUNTER') and (translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOOD COURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FOODCOURT' or translate(normalize-space(${r3_destination_guess}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEW CANTEEN') and (normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' or translate(normalize-space(${r3_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FAKE-ME-CYBER') and (translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CY SEMINAR HALL' or translate(normalize-space(${r4_caesar_decoded_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER SEMINAR HALL') and translate(normalize-space(${r4_cy_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PHY-CY' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI') and translate(normalize-space(${final_riddle2_stage_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE' and translate(normalize-space(${final_stage_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH1'</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
+🏆 You have successfully conquered every challenge, puzzle, cipher, and checkpoint on PATH 1!
+🔔 NOW RUN TO GO RING THE BELL TO WIN THE GAME! 🔔🏃💨</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Run to ring the bell to claim victory!</v>
+      </c>
+      <c r="I64" t="str">
+        <v>(normalize-space(${r2_var_a_volunteer_code}) = 'MECH-PS-1' or normalize-space(${r2_var_b_volunteer_code}) = 'ME-PB-1') and (normalize-space(${r3_decode_w1}) = 'HALDIRAM' and normalize-space(${r3_decode_w2}) = 'BREAK' and normalize-space(${r3_decode_w3}) = 'BOTTLE' and normalize-space(${r3_decode_w4}) = 'QUEUE' and normalize-space(${r3_decode_w5}) = 'COUNTER') and (normalize-space(${r3_destination_guess}) = 'FOOD COURT' or normalize-space(${r3_destination_guess}) = 'FOOD CANTEEN' or normalize-space(${r3_destination_guess}) = 'CANTEEN' or normalize-space(${r3_destination_guess}) = 'FOODCOURT' or normalize-space(${r3_destination_guess}) = 'NEW CANTEEN') and normalize-space(${r3_qr_scan}) = 'FAKE-ME-CYBER' and normalize-space(${r3_qr_volunteer_code}) = 'QR-HUNT-GOOD' and (normalize-space(${r4_caesar_decoded_answer}) = 'CYBER' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SECURITY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY' or normalize-space(${r4_caesar_decoded_answer}) = 'CY SEMINAR HALL' or normalize-space(${r4_caesar_decoded_answer}) = 'CYBER SEMINAR HALL') and normalize-space(${r4_start_code}) = 'START-PHY' and normalize-space(${r4_cy_volunteer_code}) = 'PHY-CY' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE' and normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH1'</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
         <v>end_group</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J65"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1513,24 +1703,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>mech_task_list</v>
+        <v>r2_variant_list</v>
       </c>
       <c r="B2" t="str">
-        <v>var1</v>
+        <v>var_a</v>
       </c>
       <c r="C2" t="str">
-        <v>Variant 1: Human Shape Pose Challenge</v>
+        <v>Variant A: Human Poses</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>mech_task_list</v>
+        <v>r2_variant_list</v>
       </c>
       <c r="B3" t="str">
-        <v>var2</v>
+        <v>var_b</v>
       </c>
       <c r="C3" t="str">
-        <v>Variant 2: Paper Ball Challenge</v>
+        <v>Variant B: Paper Ball</v>
       </c>
     </row>
   </sheetData>
@@ -1566,7 +1756,7 @@
         <v>final_clue_path1</v>
       </c>
       <c r="C2" t="str">
-        <v>20260902</v>
+        <v>20260903</v>
       </c>
       <c r="D2" t="str">
         <v>default</v>

--- a/ROUTE_1_PATH1_ECE_MECH_FC_CY_AUDI/PATH1_FINAL_ODK.xlsx
+++ b/ROUTE_1_PATH1_ECE_MECH_FC_CY_AUDI/PATH1_FINAL_ODK.xlsx
@@ -483,7 +483,8 @@
 • Round 3 ➔ Round 4: Next 7 teams proceed
 • Round 4 ➔ Round 5: Next 2 teams proceed
 from each path
-⚠️ MANDATORY RESPONSE &amp; CAPS ONLY RULES:
+⚠️ STRICT PROGRESSION &amp; MANDATORY RULES:
+• Read each question properly as you cannot come back to the question once you go ahead!
 • Every single question and upload is strictly MANDATORY.
 • All text answers and volunteer clearance codes must be entered in UPPERCASE (CAPS ONLY).
 • Lowercase letters will be rejected.</v>
@@ -504,7 +505,7 @@
 Enter code in caps</v>
       </c>
       <c r="D4" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E4" t="str">
         <v>yes</v>
@@ -531,7 +532,7 @@
 Enter in caps</v>
       </c>
       <c r="D5" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E5" t="str">
         <v>yes</v>
@@ -615,7 +616,7 @@
 Enter code in caps</v>
       </c>
       <c r="D10" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E10" t="str">
         <v>yes</v>
@@ -679,7 +680,7 @@
 Enter code in caps</v>
       </c>
       <c r="D14" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E14" t="str">
         <v>yes</v>
@@ -725,7 +726,7 @@
 Enter code in caps</v>
       </c>
       <c r="D16" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E16" t="str">
         <v>yes</v>
@@ -913,7 +914,7 @@
 Enter code in caps</v>
       </c>
       <c r="D26" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E26" t="str">
         <v>yes</v>
@@ -978,7 +979,7 @@
 Enter code in caps</v>
       </c>
       <c r="D30" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E30" t="str">
         <v>yes</v>
@@ -1050,7 +1051,7 @@
 Enter code in caps</v>
       </c>
       <c r="D35" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E35" t="str">
         <v>yes</v>
@@ -1077,7 +1078,7 @@
 Enter code in caps</v>
       </c>
       <c r="D36" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E36" t="str">
         <v>yes</v>
@@ -1104,7 +1105,7 @@
 Enter code in caps</v>
       </c>
       <c r="D37" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E37" t="str">
         <v>yes</v>
@@ -1131,7 +1132,7 @@
 Enter code in caps</v>
       </c>
       <c r="D38" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E38" t="str">
         <v>yes</v>
@@ -1158,7 +1159,7 @@
 Enter code in caps</v>
       </c>
       <c r="D39" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E39" t="str">
         <v>yes</v>
@@ -1191,7 +1192,7 @@
 Enter code in caps</v>
       </c>
       <c r="D40" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E40" t="str">
         <v>yes</v>
@@ -1283,7 +1284,7 @@
 Enter code in caps</v>
       </c>
       <c r="D45" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E45" t="str">
         <v>yes</v>
@@ -1355,7 +1356,7 @@
 Enter code in caps</v>
       </c>
       <c r="D49" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E49" t="str">
         <v>yes</v>
@@ -1418,7 +1419,7 @@
 Enter code in caps</v>
       </c>
       <c r="D53" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E53" t="str">
         <v>yes</v>
@@ -1464,7 +1465,7 @@
 Enter code in caps</v>
       </c>
       <c r="D55" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E55" t="str">
         <v>yes</v>
@@ -1535,7 +1536,7 @@
 Enter code in caps</v>
       </c>
       <c r="D59" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E59" t="str">
         <v>yes</v>
@@ -1563,7 +1564,7 @@
 Enter code in caps</v>
       </c>
       <c r="D60" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E60" t="str">
         <v>yes</v>
@@ -1637,7 +1638,7 @@
 Enter code in caps</v>
       </c>
       <c r="D63" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E63" t="str">
         <v>yes</v>
